--- a/reports/pdf_change_20260918.xlsx
+++ b/reports/pdf_change_20260918.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 29억(0.6%)      당일 2026-09-18  vs  전영업일 2026-09-17      매수 4종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억      당일 2026-09-18  vs  전영업일 2026-09-17      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -895,7 +895,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 59억(1.7%)      당일 2026-09-18  vs  전영업일 2026-09-17      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억      당일 2026-09-18  vs  전영업일 2026-09-17      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1012,7 +1012,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 38억(1.5%)      당일 2026-09-18  vs  전영업일 2026-09-17      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억      당일 2026-09-18  vs  전영업일 2026-09-17      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1036,7 +1036,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 13억(0.7%)      당일 2026-09-18  vs  전영업일 2026-09-17      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억      당일 2026-09-18  vs  전영업일 2026-09-17      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1060,7 +1060,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 2억(0.6%)      당일 2026-09-18  vs  전영업일 2026-09-17      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억      당일 2026-09-18  vs  전영업일 2026-09-17      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1309,7 +1309,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 486억   ·   현금 3억(0.6%)      당일 2026-09-18  vs  전영업일 2026-09-17      매수 3종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 486억      당일 2026-09-18  vs  전영업일 2026-09-17      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
